--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olivia\Documents\EPS_Models by Region\RMI\RMI_all_states\AL\trans\TTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE2850B2-8565-43B5-BC4D-D8DFB5C31094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D53E092-2E66-41CA-BEEE-8CEBE277CDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12735" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32925" yWindow="1350" windowWidth="23010" windowHeight="13800" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <sheet name="TTS-motorbikes-psgr" sheetId="17" r:id="rId20"/>
     <sheet name="TTS-motorbikes-frgt" sheetId="18" r:id="rId21"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="987">
   <si>
     <t>Source:</t>
   </si>
@@ -3012,9 +3012,6 @@
   </si>
   <si>
     <t>historical data.</t>
-  </si>
-  <si>
-    <t>Alabama</t>
   </si>
 </sst>
 </file>
@@ -3819,7 +3816,7 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3896,7 +3893,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="88">
     <cellStyle name="20% - Accent1" xfId="28" builtinId="30" customBuiltin="1"/>
@@ -6411,9 +6407,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6451,9 +6447,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6486,26 +6482,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6538,26 +6517,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6731,24 +6693,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C130"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="56.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="B1" t="s">
-        <v>987</v>
-      </c>
-      <c r="C1" s="48">
-        <v>44907</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -6756,57 +6712,57 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>2021</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>968</v>
       </c>
@@ -7679,127 +7635,127 @@
       </c>
       <c r="B4">
         <f>Data!H12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <f>Data!I12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <f>Data!J12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f>Data!K12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <f>Data!L12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <f>Data!M12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <f>Data!N12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <f>Data!O12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <f>Data!P12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <f>Data!Q12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <f>Data!R12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4">
         <f>Data!S12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N4">
         <f>Data!T12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O4">
         <f>Data!U12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P4">
         <f>Data!V12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q4">
         <f>Data!W12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R4">
         <f>Data!X12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S4">
         <f>Data!Y12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T4">
         <f>Data!Z12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U4">
         <f>Data!AA12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V4">
         <f>Data!AB12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W4">
         <f>Data!AC12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X4">
         <f>Data!AD12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4">
         <f>Data!AE12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z4">
         <f>Data!AF12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA4">
         <f>Data!AG12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB4">
         <f>Data!AH12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC4">
         <f>Data!AI12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD4">
         <f>Data!AJ12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE4">
         <f>Data!AK12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF4">
         <f>Data!AL12</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -10822,97 +10778,128 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <f>Data!H33</f>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <f>Data!I33</f>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <f>Data!J33</f>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <f>Data!K33</f>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <f>Data!L33</f>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <f>Data!M33</f>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <f>Data!N33</f>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <f>Data!O33</f>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <f>Data!P33</f>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <f>Data!Q33</f>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <f>Data!R33</f>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <f>Data!S33</f>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <f>Data!T33</f>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>2</v>
+        <f>Data!U33</f>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <f>Data!V33</f>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <f>Data!W33</f>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <f>Data!X33</f>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <f>Data!Y33</f>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <f>Data!Z33</f>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <f>Data!AA33</f>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <f>Data!AB33</f>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>2</v>
+        <f>Data!AC33</f>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <f>Data!AD33</f>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>2</v>
+        <f>Data!AE33</f>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>2</v>
+        <f>Data!AF33</f>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>2</v>
+        <f>Data!AG33</f>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>2</v>
+        <f>Data!AH33</f>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>2</v>
+        <f>Data!AI33</f>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>2</v>
+        <f>Data!AJ33</f>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>2</v>
+        <f>Data!AK33</f>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>2</v>
+        <f>Data!AL33</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -17727,7 +17714,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AJ76"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="E1">
@@ -25950,7 +25937,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AJ59"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1">
@@ -30524,7 +30511,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E495E93-490C-4630-BB04-9B57B46A213E}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -31679,7 +31666,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AJ262"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1">
@@ -55698,10 +55685,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="17.140625" customWidth="1"/>
@@ -55911,16 +55898,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="17.140625" customWidth="1"/>
     <col min="6" max="8" width="23.28515625" customWidth="1"/>
     <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -58654,10 +58641,10 @@
         <v>3</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" s="7" t="str">
         <f>IF(D12=E12,"n/a",IF(OR(C12="battery electric vehicle",C12="natural gas vehicle",C12="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -58665,127 +58652,127 @@
       </c>
       <c r="H12" s="22">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,I$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,J$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,K$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,L$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,M$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,N$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,O$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,P$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,Q$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,R$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,S$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,T$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,U$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,V$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,W$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,X$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,Y$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,Z$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AA$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AB$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AC$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AD$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AE$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AF$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AG$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AH$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AI$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AJ$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AK$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AL$9))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.25">

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\TTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AL\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D53E092-2E66-41CA-BEEE-8CEBE277CDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD6BB25E-DD3D-42A7-9D9A-DC550722A046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32925" yWindow="1350" windowWidth="23010" windowHeight="13800" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="1110" windowWidth="13035" windowHeight="16890" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="988">
   <si>
     <t>Source:</t>
   </si>
@@ -3012,6 +3012,9 @@
   </si>
   <si>
     <t>historical data.</t>
+  </si>
+  <si>
+    <t>Alabama</t>
   </si>
 </sst>
 </file>
@@ -3816,7 +3819,7 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3893,6 +3896,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="88">
     <cellStyle name="20% - Accent1" xfId="28" builtinId="30" customBuiltin="1"/>
@@ -6693,18 +6697,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B130"/>
+  <dimension ref="A1:C130"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="56.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>905</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>987</v>
+      </c>
+      <c r="C1" s="48">
+        <v>45258</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -6712,57 +6722,57 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>2021</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>968</v>
       </c>
@@ -7635,127 +7645,127 @@
       </c>
       <c r="B4">
         <f>Data!H12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <f>Data!I12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <f>Data!J12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <f>Data!K12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <f>Data!L12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <f>Data!M12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <f>Data!N12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <f>Data!O12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <f>Data!P12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4">
         <f>Data!Q12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <f>Data!R12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <f>Data!S12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N4">
         <f>Data!T12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <f>Data!U12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P4">
         <f>Data!V12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q4">
         <f>Data!W12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R4">
         <f>Data!X12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S4">
         <f>Data!Y12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T4">
         <f>Data!Z12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U4">
         <f>Data!AA12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V4">
         <f>Data!AB12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W4">
         <f>Data!AC12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X4">
         <f>Data!AD12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y4">
         <f>Data!AE12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z4">
         <f>Data!AF12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA4">
         <f>Data!AG12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB4">
         <f>Data!AH12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC4">
         <f>Data!AI12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD4">
         <f>Data!AJ12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE4">
         <f>Data!AK12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF4">
         <f>Data!AL12</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -10778,128 +10788,97 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <f>Data!H33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="C4">
-        <f>Data!I33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="D4">
-        <f>Data!J33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="E4">
-        <f>Data!K33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F4">
-        <f>Data!L33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G4">
-        <f>Data!M33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H4">
-        <f>Data!N33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I4">
-        <f>Data!O33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J4">
-        <f>Data!P33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="K4">
-        <f>Data!Q33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="L4">
-        <f>Data!R33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="M4">
-        <f>Data!S33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="N4">
-        <f>Data!T33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="O4">
-        <f>Data!U33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="P4">
-        <f>Data!V33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q4">
-        <f>Data!W33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="R4">
-        <f>Data!X33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="S4">
-        <f>Data!Y33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="T4">
-        <f>Data!Z33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="U4">
-        <f>Data!AA33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="V4">
-        <f>Data!AB33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="W4">
-        <f>Data!AC33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="X4">
-        <f>Data!AD33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Y4">
-        <f>Data!AE33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Z4">
-        <f>Data!AF33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AA4">
-        <f>Data!AG33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AB4">
-        <f>Data!AH33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AC4">
-        <f>Data!AI33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AD4">
-        <f>Data!AJ33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AE4">
-        <f>Data!AK33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AF4">
-        <f>Data!AL33</f>
-        <v>0</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -17714,7 +17693,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AJ76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="E1">
@@ -25937,7 +25916,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AJ59"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1">
@@ -30511,7 +30490,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E495E93-490C-4630-BB04-9B57B46A213E}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -31666,7 +31645,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AJ262"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1">
@@ -55685,10 +55664,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="17.140625" customWidth="1"/>
@@ -55898,16 +55877,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="17.140625" customWidth="1"/>
     <col min="6" max="8" width="23.28515625" customWidth="1"/>
     <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -58641,10 +58620,10 @@
         <v>3</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" s="7" t="str">
         <f>IF(D12=E12,"n/a",IF(OR(C12="battery electric vehicle",C12="natural gas vehicle",C12="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -58652,127 +58631,127 @@
       </c>
       <c r="H12" s="22">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:I$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,I$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:J$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,J$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:K$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,K$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:L$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,L$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:M$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,M$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:N$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,N$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:O$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,O$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:P$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,P$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:Q$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,Q$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:R$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,R$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:S$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,S$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:T$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,T$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:U$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,U$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:V$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,V$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:W$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,W$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:X$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,X$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:Y$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,Y$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:Z$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,Z$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AA$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AA$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AB$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AB$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AC$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AC$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AD$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AD$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AE$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AE$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AF$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AF$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AG$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AG$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AH$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AH$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AI$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AI$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AJ$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AJ$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AK$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AK$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL12">
         <f>IF($F12="s-curve",$D12+($E12-$D12)*$I$2/(1+EXP($I$3*(COUNT($H$9:AL$9)+$I$4))),TREND($D12:$E12,$D$9:$E$9,AL$9))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.25">

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3E9D49-3C08-403B-955B-13A3673F78ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1690D90-B88A-4916-A6CE-CC1A8F7A5860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -4728,91 +4728,91 @@
                   <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.21838189592802051</c:v>
+                  <c:v>0.22583637175876042</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.23794069854205344</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.27627957191928759</c:v>
+                  <c:v>0.25531073627467749</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3459404190450851</c:v>
+                  <c:v>0.27980039129574813</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.45665704065968565</c:v>
+                  <c:v>0.31348085192039021</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.60000000000000009</c:v>
+                  <c:v>0.35825288915313458</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.74334295934031447</c:v>
+                  <c:v>0.41515313709599611</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.85405958095491497</c:v>
+                  <c:v>0.48347495501936366</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.92372042808071253</c:v>
+                  <c:v>0.56013280215001782</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.63986719784998236</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.71652504498063641</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.78484686290400396</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.84174711084686549</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.88651914807960996</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.92019960870425188</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.94468926372532258</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>0.9620593014579466</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.98161810407197958</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.99121044589552554</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.99582389944515337</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.99802190147469227</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.99906439178795559</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.99955777709046112</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.9997910477447236</c:v>
-                </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.99990128433921099</c:v>
+                  <c:v>0.97416362824123981</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.99995336698747117</c:v>
+                  <c:v>0.98249498325109563</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.99997797144710843</c:v>
+                  <c:v>0.98818077464538168</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.99998959429722678</c:v>
+                  <c:v>0.9920385585064766</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.99999508466031828</c:v>
+                  <c:v>0.99464571926057221</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.99999767815041185</c:v>
+                  <c:v>0.99640298147124717</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.99999890323423446</c:v>
+                  <c:v>0.99758526694023342</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.99999948192416133</c:v>
+                  <c:v>0.99837974368876004</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.99999975527821849</c:v>
+                  <c:v>0.99891318403965701</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.99999988440159693</c:v>
+                  <c:v>0.99927115904447961</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.99999994539517689</c:v>
+                  <c:v>0.99951129651245263</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.99999997420650688</c:v>
+                  <c:v>0.99967234626801127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4994,6 +4994,347 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Data!$I$10:$AL$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="General">
+                  <c:v>6.8830969931196209E-2</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="General">
+                  <c:v>7.8745282392924873E-2</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="General">
+                  <c:v>9.3149431265043575E-2</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="General">
+                  <c:v>0.11381977616686616</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="General">
+                  <c:v>0.14296246564194026</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="General">
+                  <c:v>0.18304221378526436</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="General">
+                  <c:v>0.23632093809223015</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="General">
+                  <c:v>0.30403223314423533</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="General">
+                  <c:v>0.38533519647304271</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="General">
+                  <c:v>0.47655803455852103</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="General">
+                  <c:v>0.57144196544147907</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="General">
+                  <c:v>0.66266480352695722</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="General">
+                  <c:v>0.7439677668557646</c:v>
+                </c:pt>
+                <c:pt idx="15" formatCode="General">
+                  <c:v>0.81167906190776995</c:v>
+                </c:pt>
+                <c:pt idx="16" formatCode="General">
+                  <c:v>0.86495778621473574</c:v>
+                </c:pt>
+                <c:pt idx="17" formatCode="General">
+                  <c:v>0.90503753435805978</c:v>
+                </c:pt>
+                <c:pt idx="18" formatCode="General">
+                  <c:v>0.93418022383313393</c:v>
+                </c:pt>
+                <c:pt idx="19" formatCode="General">
+                  <c:v>0.95485056873495655</c:v>
+                </c:pt>
+                <c:pt idx="20" formatCode="General">
+                  <c:v>0.96925471760707527</c:v>
+                </c:pt>
+                <c:pt idx="21" formatCode="General">
+                  <c:v>0.97916903006880374</c:v>
+                </c:pt>
+                <c:pt idx="22" formatCode="General">
+                  <c:v>0.98593512182800402</c:v>
+                </c:pt>
+                <c:pt idx="23" formatCode="General">
+                  <c:v>0.99052588462270719</c:v>
+                </c:pt>
+                <c:pt idx="24" formatCode="General">
+                  <c:v>0.99362840592008095</c:v>
+                </c:pt>
+                <c:pt idx="25" formatCode="General">
+                  <c:v>0.99571954795078399</c:v>
+                </c:pt>
+                <c:pt idx="26" formatCode="General">
+                  <c:v>0.99712646765887769</c:v>
+                </c:pt>
+                <c:pt idx="27" formatCode="General">
+                  <c:v>0.99807189498962445</c:v>
+                </c:pt>
+                <c:pt idx="28" formatCode="General">
+                  <c:v>0.99870668900719173</c:v>
+                </c:pt>
+                <c:pt idx="29" formatCode="General">
+                  <c:v>0.99913267926293059</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2CD7-4B7A-BC10-BFBD94963D9F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="584510703"/>
+        <c:axId val="589151247"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="584510703"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="589151247"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="589151247"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="584510703"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -5035,6 +5376,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -6106,6 +6487,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -6180,6 +7077,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>136525</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37611677-E89A-3C1B-D779-903087F49626}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -7163,11 +8096,11 @@
       </c>
       <c r="D2">
         <f>Data!K10</f>
-        <v>5.8459569384324707E-2</v>
+        <v>6.8830969931196209E-2</v>
       </c>
       <c r="E2">
         <f>Data!L10</f>
-        <v>6.9874456154344386E-2</v>
+        <v>7.8745282392924873E-2</v>
       </c>
       <c r="F2">
         <f>Data!M10</f>
@@ -7175,103 +8108,103 @@
       </c>
       <c r="G2">
         <f>Data!N10</f>
-        <v>0.13877269058395222</v>
+        <v>0.11381977616686616</v>
       </c>
       <c r="H2">
         <f>Data!O10</f>
-        <v>0.22166909866365125</v>
+        <v>0.14296246564194026</v>
       </c>
       <c r="I2">
         <f>Data!P10</f>
-        <v>0.35342187838502587</v>
+        <v>0.18304221378526436</v>
       </c>
       <c r="J2">
         <f>Data!Q10</f>
-        <v>0.52400000000000002</v>
+        <v>0.23632093809223015</v>
       </c>
       <c r="K2">
         <f>Data!R10</f>
-        <v>0.69457812161497412</v>
+        <v>0.30403223314423533</v>
       </c>
       <c r="L2">
         <f>Data!S10</f>
-        <v>0.82633090133634868</v>
+        <v>0.38533519647304271</v>
       </c>
       <c r="M2">
         <f>Data!T10</f>
-        <v>0.90922730941604779</v>
+        <v>0.47655803455852103</v>
       </c>
       <c r="N2">
         <f>Data!U10</f>
-        <v>0.95485056873495655</v>
+        <v>0.57144196544147907</v>
       </c>
       <c r="O2">
         <f>Data!V10</f>
-        <v>0.97812554384565553</v>
+        <v>0.66266480352695722</v>
       </c>
       <c r="P2">
         <f>Data!W10</f>
-        <v>1</v>
+        <v>0.7439677668557646</v>
       </c>
       <c r="Q2">
         <f>Data!X10</f>
-        <v>1</v>
+        <v>0.81167906190776995</v>
       </c>
       <c r="R2">
         <f>Data!Y10</f>
-        <v>1</v>
+        <v>0.86495778621473574</v>
       </c>
       <c r="S2">
         <f>Data!Z10</f>
-        <v>1</v>
+        <v>0.90503753435805978</v>
       </c>
       <c r="T2">
         <f>Data!AA10</f>
-        <v>1</v>
+        <v>0.93418022383313393</v>
       </c>
       <c r="U2">
         <f>Data!AB10</f>
-        <v>1</v>
+        <v>0.95485056873495655</v>
       </c>
       <c r="V2">
         <f>Data!AC10</f>
-        <v>1</v>
+        <v>0.96925471760707527</v>
       </c>
       <c r="W2">
         <f>Data!AD10</f>
-        <v>1</v>
+        <v>0.97916903006880374</v>
       </c>
       <c r="X2">
         <f>Data!AE10</f>
-        <v>1</v>
+        <v>0.98593512182800402</v>
       </c>
       <c r="Y2">
         <f>Data!AF10</f>
-        <v>1</v>
+        <v>0.99052588462270719</v>
       </c>
       <c r="Z2">
         <f>Data!AG10</f>
-        <v>1</v>
+        <v>0.99362840592008095</v>
       </c>
       <c r="AA2">
         <f>Data!AH10</f>
-        <v>1</v>
+        <v>0.99571954795078399</v>
       </c>
       <c r="AB2">
         <f>Data!AI10</f>
-        <v>1</v>
+        <v>0.99712646765887769</v>
       </c>
       <c r="AC2">
         <f>Data!AJ10</f>
-        <v>1</v>
+        <v>0.99807189498962445</v>
       </c>
       <c r="AD2">
         <f>Data!AK10</f>
-        <v>1</v>
+        <v>0.99870668900719173</v>
       </c>
       <c r="AE2">
         <f>Data!AL10</f>
-        <v>1</v>
+        <v>0.99913267926293059</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.35">
@@ -7667,111 +8600,111 @@
       </c>
       <c r="E6">
         <f>Data!L14</f>
-        <v>1.2004677525762598E-2</v>
+        <v>1.0903813654420566E-2</v>
       </c>
       <c r="F6">
         <f>Data!M14</f>
-        <v>1.5661871999866968E-2</v>
+        <v>1.2189520543026775E-2</v>
       </c>
       <c r="G6">
         <f>Data!N14</f>
-        <v>2.1474494634633495E-2</v>
+        <v>1.3957744725820488E-2</v>
       </c>
       <c r="H6">
         <f>Data!O14</f>
-        <v>2.9000000000000001E-2</v>
+        <v>1.6308276680539566E-2</v>
       </c>
       <c r="I6">
         <f>Data!P14</f>
-        <v>3.6525505365366501E-2</v>
+        <v>1.9295539697539797E-2</v>
       </c>
       <c r="J6">
         <f>Data!Q14</f>
-        <v>4.2338128000133035E-2</v>
+        <v>2.2882435138516594E-2</v>
       </c>
       <c r="K6">
         <f>Data!R14</f>
-        <v>4.5995322474237404E-2</v>
+        <v>2.6906972112875932E-2</v>
       </c>
       <c r="L6">
         <f>Data!S14</f>
-        <v>4.8008113326542201E-2</v>
+        <v>3.1093027887124074E-2</v>
       </c>
       <c r="M6">
         <f>Data!T14</f>
-        <v>4.9034950463778926E-2</v>
+        <v>3.5117564861483409E-2</v>
       </c>
       <c r="N6">
         <f>Data!U14</f>
-        <v>4.953854840951509E-2</v>
+        <v>3.8704460302460206E-2</v>
       </c>
       <c r="O6">
         <f>Data!V14</f>
-        <v>4.9780754720870554E-2</v>
+        <v>4.1691723319460437E-2</v>
       </c>
       <c r="P6">
         <f>Data!W14</f>
-        <v>4.9896149827421347E-2</v>
+        <v>4.4042255274179515E-2</v>
       </c>
       <c r="Q6">
         <f>Data!X14</f>
-        <v>4.9950880568867671E-2</v>
+        <v>4.5810479456973224E-2</v>
       </c>
       <c r="R6">
         <f>Data!Y14</f>
-        <v>4.9976783297249215E-2</v>
+        <v>4.7096186345579438E-2</v>
       </c>
       <c r="S6">
         <f>Data!Z14</f>
-        <v>4.9989030006597983E-2</v>
+        <v>4.8008113326542201E-2</v>
       </c>
       <c r="T6">
         <f>Data!AA14</f>
-        <v>4.9994817427808577E-2</v>
+        <v>4.8643590482665089E-2</v>
       </c>
       <c r="U6">
         <f>Data!AB14</f>
-        <v>4.9997551766842237E-2</v>
+        <v>4.9080986620682519E-2</v>
       </c>
       <c r="V6">
         <f>Data!AC14</f>
-        <v>4.9998843500973188E-2</v>
+        <v>4.9379490668882538E-2</v>
       </c>
       <c r="W6">
         <f>Data!AD14</f>
-        <v>4.9999453700604407E-2</v>
+        <v>4.9582024321590021E-2</v>
       </c>
       <c r="X6">
         <f>Data!AE14</f>
-        <v>4.9999741944666706E-2</v>
+        <v>4.9718900261180046E-2</v>
       </c>
       <c r="Y6">
         <f>Data!AF14</f>
-        <v>4.9999878102896626E-2</v>
+        <v>4.9811156527240476E-2</v>
       </c>
       <c r="Z6">
         <f>Data!AG14</f>
-        <v>4.9999942419797314E-2</v>
+        <v>4.9873226514362254E-2</v>
       </c>
       <c r="AA6">
         <f>Data!AH14</f>
-        <v>4.9999972801018477E-2</v>
+        <v>4.9914936543659902E-2</v>
       </c>
       <c r="AB6">
         <f>Data!AI14</f>
-        <v>4.9999987152106469E-2</v>
+        <v>4.9942942162081991E-2</v>
       </c>
       <c r="AC6">
         <f>Data!AJ14</f>
-        <v>4.9999993931083841E-2</v>
+        <v>4.9961735849835175E-2</v>
       </c>
       <c r="AD6">
         <f>Data!AK14</f>
-        <v>4.9999997133246779E-2</v>
+        <v>4.9974343066903758E-2</v>
       </c>
       <c r="AE6">
         <f>Data!AL14</f>
-        <v>4.9999998645841613E-2</v>
+        <v>4.9982798179070587E-2</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.35">
@@ -8175,7 +9108,7 @@
       </c>
       <c r="C2">
         <f>Data!J17</f>
-        <v>0.21838189592802051</v>
+        <v>0.22583637175876042</v>
       </c>
       <c r="D2">
         <f>Data!K17</f>
@@ -8183,111 +9116,111 @@
       </c>
       <c r="E2">
         <f>Data!L17</f>
-        <v>0.27627957191928759</v>
+        <v>0.25531073627467749</v>
       </c>
       <c r="F2">
         <f>Data!M17</f>
-        <v>0.3459404190450851</v>
+        <v>0.27980039129574813</v>
       </c>
       <c r="G2">
         <f>Data!N17</f>
-        <v>0.45665704065968565</v>
+        <v>0.31348085192039021</v>
       </c>
       <c r="H2">
         <f>Data!O17</f>
-        <v>0.60000000000000009</v>
+        <v>0.35825288915313458</v>
       </c>
       <c r="I2">
         <f>Data!P17</f>
-        <v>0.74334295934031447</v>
+        <v>0.41515313709599611</v>
       </c>
       <c r="J2">
         <f>Data!Q17</f>
-        <v>0.85405958095491497</v>
+        <v>0.48347495501936366</v>
       </c>
       <c r="K2">
         <f>Data!R17</f>
-        <v>0.92372042808071253</v>
+        <v>0.56013280215001782</v>
       </c>
       <c r="L2">
         <f>Data!S17</f>
-        <v>0.9620593014579466</v>
+        <v>0.63986719784998236</v>
       </c>
       <c r="M2">
         <f>Data!T17</f>
-        <v>0.98161810407197958</v>
+        <v>0.71652504498063641</v>
       </c>
       <c r="N2">
         <f>Data!U17</f>
-        <v>0.99121044589552554</v>
+        <v>0.78484686290400396</v>
       </c>
       <c r="O2">
         <f>Data!V17</f>
-        <v>0.99582389944515337</v>
+        <v>0.84174711084686549</v>
       </c>
       <c r="P2">
         <f>Data!W17</f>
-        <v>0.99802190147469227</v>
+        <v>0.88651914807960996</v>
       </c>
       <c r="Q2">
         <f>Data!X17</f>
-        <v>0.99906439178795559</v>
+        <v>0.92019960870425188</v>
       </c>
       <c r="R2">
         <f>Data!Y17</f>
-        <v>0.99955777709046112</v>
+        <v>0.94468926372532258</v>
       </c>
       <c r="S2">
         <f>Data!Z17</f>
-        <v>0.9997910477447236</v>
+        <v>0.9620593014579466</v>
       </c>
       <c r="T2">
         <f>Data!AA17</f>
-        <v>0.99990128433921099</v>
+        <v>0.97416362824123981</v>
       </c>
       <c r="U2">
         <f>Data!AB17</f>
-        <v>0.99995336698747117</v>
+        <v>0.98249498325109563</v>
       </c>
       <c r="V2">
         <f>Data!AC17</f>
-        <v>0.99997797144710843</v>
+        <v>0.98818077464538168</v>
       </c>
       <c r="W2">
         <f>Data!AD17</f>
-        <v>0.99998959429722678</v>
+        <v>0.9920385585064766</v>
       </c>
       <c r="X2">
         <f>Data!AE17</f>
-        <v>0.99999508466031828</v>
+        <v>0.99464571926057221</v>
       </c>
       <c r="Y2">
         <f>Data!AF17</f>
-        <v>0.99999767815041185</v>
+        <v>0.99640298147124717</v>
       </c>
       <c r="Z2">
         <f>Data!AG17</f>
-        <v>0.99999890323423446</v>
+        <v>0.99758526694023342</v>
       </c>
       <c r="AA2">
         <f>Data!AH17</f>
-        <v>0.99999948192416133</v>
+        <v>0.99837974368876004</v>
       </c>
       <c r="AB2">
         <f>Data!AI17</f>
-        <v>0.99999975527821849</v>
+        <v>0.99891318403965701</v>
       </c>
       <c r="AC2">
         <f>Data!AJ17</f>
-        <v>0.99999988440159693</v>
+        <v>0.99927115904447961</v>
       </c>
       <c r="AD2">
         <f>Data!AK17</f>
-        <v>0.99999994539517689</v>
+        <v>0.99951129651245263</v>
       </c>
       <c r="AE2">
         <f>Data!AL17</f>
-        <v>0.99999997420650688</v>
+        <v>0.99967234626801127</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.35">
@@ -9195,11 +10128,11 @@
       </c>
       <c r="D2">
         <f>Data!K24</f>
-        <v>0.60439477705223721</v>
+        <v>0.60875250837445216</v>
       </c>
       <c r="E2">
         <f>Data!L24</f>
-        <v>0.60919094796401019</v>
+        <v>0.61291818587938018</v>
       </c>
       <c r="F2">
         <f>Data!M24</f>
@@ -9207,103 +10140,103 @@
       </c>
       <c r="G2">
         <f>Data!N24</f>
-        <v>0.63813978595964382</v>
+        <v>0.62765536813733869</v>
       </c>
       <c r="H2">
         <f>Data!O24</f>
-        <v>0.6729702095225425</v>
+        <v>0.63990019564787404</v>
       </c>
       <c r="I2">
         <f>Data!P24</f>
-        <v>0.72832852032984285</v>
+        <v>0.65674042596019511</v>
       </c>
       <c r="J2">
         <f>Data!Q24</f>
-        <v>0.8</v>
+        <v>0.67912644457656723</v>
       </c>
       <c r="K2">
         <f>Data!R24</f>
-        <v>0.87167147967015723</v>
+        <v>0.707576568547998</v>
       </c>
       <c r="L2">
         <f>Data!S24</f>
-        <v>0.92702979047745737</v>
+        <v>0.74173747750968178</v>
       </c>
       <c r="M2">
         <f>Data!T24</f>
-        <v>0.96186021404035627</v>
+        <v>0.78006640107500891</v>
       </c>
       <c r="N2">
         <f>Data!U24</f>
-        <v>0.9810296507289733</v>
+        <v>0.81993359892499118</v>
       </c>
       <c r="O2">
         <f>Data!V24</f>
-        <v>0.99080905203598979</v>
+        <v>0.8582625224903182</v>
       </c>
       <c r="P2">
         <f>Data!W24</f>
-        <v>0.99560522294776277</v>
+        <v>0.89242343145200187</v>
       </c>
       <c r="Q2">
         <f>Data!X24</f>
-        <v>0.99791194972257657</v>
+        <v>0.92087355542343274</v>
       </c>
       <c r="R2">
         <f>Data!Y24</f>
-        <v>0.99901095073734614</v>
+        <v>0.94325957403980487</v>
       </c>
       <c r="S2">
         <f>Data!Z24</f>
-        <v>0.99953219589397779</v>
+        <v>0.96009980435212594</v>
       </c>
       <c r="T2">
         <f>Data!AA24</f>
-        <v>0.99977888854523056</v>
+        <v>0.97234463186266129</v>
       </c>
       <c r="U2">
         <f>Data!AB24</f>
-        <v>0.99989552387236169</v>
+        <v>0.9810296507289733</v>
       </c>
       <c r="V2">
         <f>Data!AC24</f>
-        <v>0.9999506421696055</v>
+        <v>0.9870818141206199</v>
       </c>
       <c r="W2">
         <f>Data!AD24</f>
-        <v>0.99997668349373559</v>
+        <v>0.99124749162554782</v>
       </c>
       <c r="X2">
         <f>Data!AE24</f>
-        <v>0.99998898572355421</v>
+        <v>0.99409038732269073</v>
       </c>
       <c r="Y2">
         <f>Data!AF24</f>
-        <v>0.99999479714861339</v>
+        <v>0.9960192792532383</v>
       </c>
       <c r="Z2">
         <f>Data!AG24</f>
-        <v>0.99999754233015903</v>
+        <v>0.99732285963028611</v>
       </c>
       <c r="AA2">
         <f>Data!AH24</f>
-        <v>0.99999883907520593</v>
+        <v>0.99820149073562359</v>
       </c>
       <c r="AB2">
         <f>Data!AI24</f>
-        <v>0.99999945161711723</v>
+        <v>0.99879263347011671</v>
       </c>
       <c r="AC2">
         <f>Data!AJ24</f>
-        <v>0.99999974096208066</v>
+        <v>0.99918987184438002</v>
       </c>
       <c r="AD2">
         <f>Data!AK24</f>
-        <v>0.99999987763910925</v>
+        <v>0.99945659201982839</v>
       </c>
       <c r="AE2">
         <f>Data!AL24</f>
-        <v>0.99999994220079846</v>
+        <v>0.9996355795222398</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.35">
@@ -23663,7 +24596,7 @@
       </c>
       <c r="C2">
         <f>Data!J80</f>
-        <v>2.2977369910025615E-2</v>
+        <v>3.2295464698450495E-2</v>
       </c>
       <c r="D2">
         <f>Data!K80</f>
@@ -23671,111 +24604,111 @@
       </c>
       <c r="E2">
         <f>Data!L80</f>
-        <v>9.534946489910949E-2</v>
+        <v>6.9138420343346815E-2</v>
       </c>
       <c r="F2">
         <f>Data!M80</f>
-        <v>0.18242552380635635</v>
+        <v>9.9750489119685135E-2</v>
       </c>
       <c r="G2">
         <f>Data!N80</f>
-        <v>0.32082130082460703</v>
+        <v>0.14185106490048777</v>
       </c>
       <c r="H2">
         <f>Data!O80</f>
-        <v>0.5</v>
+        <v>0.19781611144141822</v>
       </c>
       <c r="I2">
         <f>Data!P80</f>
-        <v>0.67917869917539297</v>
+        <v>0.2689414213699951</v>
       </c>
       <c r="J2">
         <f>Data!Q80</f>
-        <v>0.81757447619364365</v>
+        <v>0.35434369377420455</v>
       </c>
       <c r="K2">
         <f>Data!R80</f>
-        <v>0.90465053510089055</v>
+        <v>0.45016600268752216</v>
       </c>
       <c r="L2">
         <f>Data!S80</f>
-        <v>0.95257412682243336</v>
+        <v>0.54983399731247795</v>
       </c>
       <c r="M2">
         <f>Data!T80</f>
-        <v>0.97702263008997436</v>
+        <v>0.6456563062257954</v>
       </c>
       <c r="N2">
         <f>Data!U80</f>
-        <v>0.98901305736940681</v>
+        <v>0.7310585786300049</v>
       </c>
       <c r="O2">
         <f>Data!V80</f>
-        <v>0.99477987430644166</v>
+        <v>0.8021838885585818</v>
       </c>
       <c r="P2">
         <f>Data!W80</f>
-        <v>0.99752737684336534</v>
+        <v>0.85814893509951229</v>
       </c>
       <c r="Q2">
         <f>Data!X80</f>
-        <v>0.99883048973494448</v>
+        <v>0.9002495108803148</v>
       </c>
       <c r="R2">
         <f>Data!Y80</f>
-        <v>0.9994472213630764</v>
+        <v>0.93086157965665328</v>
       </c>
       <c r="S2">
         <f>Data!Z80</f>
-        <v>0.99973880968090434</v>
+        <v>0.95257412682243336</v>
       </c>
       <c r="T2">
         <f>Data!AA80</f>
-        <v>0.99987660542401369</v>
+        <v>0.96770453530154954</v>
       </c>
       <c r="U2">
         <f>Data!AB80</f>
-        <v>0.99994170873433885</v>
+        <v>0.97811872906386943</v>
       </c>
       <c r="V2">
         <f>Data!AC80</f>
-        <v>0.99997246430888531</v>
+        <v>0.98522596830672693</v>
       </c>
       <c r="W2">
         <f>Data!AD80</f>
-        <v>0.99998699287153348</v>
+        <v>0.99004819813309575</v>
       </c>
       <c r="X2">
         <f>Data!AE80</f>
-        <v>0.99999385582539779</v>
+        <v>0.99330714907571527</v>
       </c>
       <c r="Y2">
         <f>Data!AF80</f>
-        <v>0.99999709768801481</v>
+        <v>0.99550372683905886</v>
       </c>
       <c r="Z2">
         <f>Data!AG80</f>
-        <v>0.99999862904279302</v>
+        <v>0.99698158367529166</v>
       </c>
       <c r="AA2">
         <f>Data!AH80</f>
-        <v>0.99999935240520166</v>
+        <v>0.9979746796109501</v>
       </c>
       <c r="AB2">
         <f>Data!AI80</f>
-        <v>0.99999969409777301</v>
+        <v>0.9986414800495711</v>
       </c>
       <c r="AC2">
         <f>Data!AJ80</f>
-        <v>0.99999985550199622</v>
+        <v>0.9990889488055994</v>
       </c>
       <c r="AD2">
         <f>Data!AK80</f>
-        <v>0.99999993174397095</v>
+        <v>0.99938912064056562</v>
       </c>
       <c r="AE2">
         <f>Data!AL80</f>
-        <v>0.9999999677581336</v>
+        <v>0.99959043283501392</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.35">
@@ -62373,7 +63306,7 @@
         <v>99</v>
       </c>
       <c r="O3" s="19">
-        <v>-0.75</v>
+        <v>-0.4</v>
       </c>
       <c r="Q3" s="9" t="s">
         <v>99</v>
@@ -62396,7 +63329,7 @@
         <v>100</v>
       </c>
       <c r="O4" s="20">
-        <v>-7</v>
+        <v>-10.5</v>
       </c>
       <c r="Q4" s="10" t="s">
         <v>100</v>
@@ -62624,11 +63557,11 @@
       </c>
       <c r="K10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:K$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,K$9))</f>
-        <v>5.8459569384324707E-2</v>
+        <v>6.8830969931196209E-2</v>
       </c>
       <c r="L10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:L$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,L$9))</f>
-        <v>6.9874456154344386E-2</v>
+        <v>7.8745282392924873E-2</v>
       </c>
       <c r="M10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:M$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,M$9))</f>
@@ -62636,87 +63569,103 @@
       </c>
       <c r="N10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:N$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,N$9))</f>
-        <v>0.13877269058395222</v>
+        <v>0.11381977616686616</v>
       </c>
       <c r="O10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:O$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,O$9))</f>
-        <v>0.22166909866365125</v>
+        <v>0.14296246564194026</v>
       </c>
       <c r="P10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:P$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,P$9))</f>
-        <v>0.35342187838502587</v>
+        <v>0.18304221378526436</v>
       </c>
       <c r="Q10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Q$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Q$9))</f>
-        <v>0.52400000000000002</v>
+        <v>0.23632093809223015</v>
       </c>
       <c r="R10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:R$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,R$9))</f>
-        <v>0.69457812161497412</v>
+        <v>0.30403223314423533</v>
       </c>
       <c r="S10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:S$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,S$9))</f>
-        <v>0.82633090133634868</v>
+        <v>0.38533519647304271</v>
       </c>
       <c r="T10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:T$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,T$9))</f>
-        <v>0.90922730941604779</v>
+        <v>0.47655803455852103</v>
       </c>
       <c r="U10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:U$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,U$9))</f>
-        <v>0.95485056873495655</v>
+        <v>0.57144196544147907</v>
       </c>
       <c r="V10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:V$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,V$9))</f>
-        <v>0.97812554384565553</v>
+        <v>0.66266480352695722</v>
       </c>
       <c r="W10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:W$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,W$9))</f>
+        <v>0.7439677668557646</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:X$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,X$9))</f>
+        <v>0.81167906190776995</v>
       </c>
       <c r="Y10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Y$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Y$9))</f>
+        <v>0.86495778621473574</v>
       </c>
       <c r="Z10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Z$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Z$9))</f>
+        <v>0.90503753435805978</v>
       </c>
       <c r="AA10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AA$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AA$9))</f>
+        <v>0.93418022383313393</v>
       </c>
       <c r="AB10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AB$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AB$9))</f>
+        <v>0.95485056873495655</v>
       </c>
       <c r="AC10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AC$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AC$9))</f>
+        <v>0.96925471760707527</v>
       </c>
       <c r="AD10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AD$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AD$9))</f>
+        <v>0.97916903006880374</v>
       </c>
       <c r="AE10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AE$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AE$9))</f>
+        <v>0.98593512182800402</v>
       </c>
       <c r="AF10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AF$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AF$9))</f>
+        <v>0.99052588462270719</v>
       </c>
       <c r="AG10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AG$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AG$9))</f>
+        <v>0.99362840592008095</v>
       </c>
       <c r="AH10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AH$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AH$9))</f>
+        <v>0.99571954795078399</v>
       </c>
       <c r="AI10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AI$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AI$9))</f>
+        <v>0.99712646765887769</v>
       </c>
       <c r="AJ10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AJ$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AJ$9))</f>
+        <v>0.99807189498962445</v>
       </c>
       <c r="AK10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AK$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AK$9))</f>
+        <v>0.99870668900719173</v>
       </c>
       <c r="AL10">
-        <v>1</v>
+        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AL$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AL$9))</f>
+        <v>0.99913267926293059</v>
       </c>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.35">
@@ -63159,111 +64108,111 @@
       </c>
       <c r="L14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:L$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,L$9))</f>
-        <v>1.2004677525762598E-2</v>
+        <v>1.0903813654420566E-2</v>
       </c>
       <c r="M14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:M$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,M$9))</f>
-        <v>1.5661871999866968E-2</v>
+        <v>1.2189520543026775E-2</v>
       </c>
       <c r="N14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:N$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,N$9))</f>
-        <v>2.1474494634633495E-2</v>
+        <v>1.3957744725820488E-2</v>
       </c>
       <c r="O14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:O$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,O$9))</f>
-        <v>2.9000000000000001E-2</v>
+        <v>1.6308276680539566E-2</v>
       </c>
       <c r="P14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:P$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,P$9))</f>
-        <v>3.6525505365366501E-2</v>
+        <v>1.9295539697539797E-2</v>
       </c>
       <c r="Q14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:Q$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,Q$9))</f>
-        <v>4.2338128000133035E-2</v>
+        <v>2.2882435138516594E-2</v>
       </c>
       <c r="R14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:R$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,R$9))</f>
-        <v>4.5995322474237404E-2</v>
+        <v>2.6906972112875932E-2</v>
       </c>
       <c r="S14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:S$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,S$9))</f>
-        <v>4.8008113326542201E-2</v>
+        <v>3.1093027887124074E-2</v>
       </c>
       <c r="T14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:T$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,T$9))</f>
-        <v>4.9034950463778926E-2</v>
+        <v>3.5117564861483409E-2</v>
       </c>
       <c r="U14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:U$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,U$9))</f>
-        <v>4.953854840951509E-2</v>
+        <v>3.8704460302460206E-2</v>
       </c>
       <c r="V14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:V$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,V$9))</f>
-        <v>4.9780754720870554E-2</v>
+        <v>4.1691723319460437E-2</v>
       </c>
       <c r="W14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:W$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,W$9))</f>
-        <v>4.9896149827421347E-2</v>
+        <v>4.4042255274179515E-2</v>
       </c>
       <c r="X14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:X$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,X$9))</f>
-        <v>4.9950880568867671E-2</v>
+        <v>4.5810479456973224E-2</v>
       </c>
       <c r="Y14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:Y$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,Y$9))</f>
-        <v>4.9976783297249215E-2</v>
+        <v>4.7096186345579438E-2</v>
       </c>
       <c r="Z14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:Z$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,Z$9))</f>
-        <v>4.9989030006597983E-2</v>
+        <v>4.8008113326542201E-2</v>
       </c>
       <c r="AA14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AA$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AA$9))</f>
-        <v>4.9994817427808577E-2</v>
+        <v>4.8643590482665089E-2</v>
       </c>
       <c r="AB14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AB$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AB$9))</f>
-        <v>4.9997551766842237E-2</v>
+        <v>4.9080986620682519E-2</v>
       </c>
       <c r="AC14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AC$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AC$9))</f>
-        <v>4.9998843500973188E-2</v>
+        <v>4.9379490668882538E-2</v>
       </c>
       <c r="AD14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AD$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AD$9))</f>
-        <v>4.9999453700604407E-2</v>
+        <v>4.9582024321590021E-2</v>
       </c>
       <c r="AE14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AE$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AE$9))</f>
-        <v>4.9999741944666706E-2</v>
+        <v>4.9718900261180046E-2</v>
       </c>
       <c r="AF14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AF$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AF$9))</f>
-        <v>4.9999878102896626E-2</v>
+        <v>4.9811156527240476E-2</v>
       </c>
       <c r="AG14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AG$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AG$9))</f>
-        <v>4.9999942419797314E-2</v>
+        <v>4.9873226514362254E-2</v>
       </c>
       <c r="AH14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AH$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AH$9))</f>
-        <v>4.9999972801018477E-2</v>
+        <v>4.9914936543659902E-2</v>
       </c>
       <c r="AI14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AI$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AI$9))</f>
-        <v>4.9999987152106469E-2</v>
+        <v>4.9942942162081991E-2</v>
       </c>
       <c r="AJ14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AJ$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AJ$9))</f>
-        <v>4.9999993931083841E-2</v>
+        <v>4.9961735849835175E-2</v>
       </c>
       <c r="AK14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AK$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AK$9))</f>
-        <v>4.9999997133246779E-2</v>
+        <v>4.9974343066903758E-2</v>
       </c>
       <c r="AL14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AL$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AL$9))</f>
-        <v>4.9999998645841613E-2</v>
+        <v>4.9982798179070587E-2</v>
       </c>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.35">
@@ -63570,7 +64519,7 @@
       </c>
       <c r="J17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:J$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,J$9))</f>
-        <v>0.21838189592802051</v>
+        <v>0.22583637175876042</v>
       </c>
       <c r="K17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:K$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,K$9))</f>
@@ -63578,111 +64527,111 @@
       </c>
       <c r="L17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:L$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,L$9))</f>
-        <v>0.27627957191928759</v>
+        <v>0.25531073627467749</v>
       </c>
       <c r="M17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:M$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,M$9))</f>
-        <v>0.3459404190450851</v>
+        <v>0.27980039129574813</v>
       </c>
       <c r="N17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:N$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,N$9))</f>
-        <v>0.45665704065968565</v>
+        <v>0.31348085192039021</v>
       </c>
       <c r="O17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:O$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,O$9))</f>
-        <v>0.60000000000000009</v>
+        <v>0.35825288915313458</v>
       </c>
       <c r="P17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:P$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,P$9))</f>
-        <v>0.74334295934031447</v>
+        <v>0.41515313709599611</v>
       </c>
       <c r="Q17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:Q$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,Q$9))</f>
-        <v>0.85405958095491497</v>
+        <v>0.48347495501936366</v>
       </c>
       <c r="R17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:R$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,R$9))</f>
-        <v>0.92372042808071253</v>
+        <v>0.56013280215001782</v>
       </c>
       <c r="S17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:S$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,S$9))</f>
-        <v>0.9620593014579466</v>
+        <v>0.63986719784998236</v>
       </c>
       <c r="T17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:T$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,T$9))</f>
-        <v>0.98161810407197958</v>
+        <v>0.71652504498063641</v>
       </c>
       <c r="U17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:U$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,U$9))</f>
-        <v>0.99121044589552554</v>
+        <v>0.78484686290400396</v>
       </c>
       <c r="V17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:V$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,V$9))</f>
-        <v>0.99582389944515337</v>
+        <v>0.84174711084686549</v>
       </c>
       <c r="W17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:W$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,W$9))</f>
-        <v>0.99802190147469227</v>
+        <v>0.88651914807960996</v>
       </c>
       <c r="X17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:X$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,X$9))</f>
-        <v>0.99906439178795559</v>
+        <v>0.92019960870425188</v>
       </c>
       <c r="Y17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:Y$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,Y$9))</f>
-        <v>0.99955777709046112</v>
+        <v>0.94468926372532258</v>
       </c>
       <c r="Z17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:Z$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,Z$9))</f>
-        <v>0.9997910477447236</v>
+        <v>0.9620593014579466</v>
       </c>
       <c r="AA17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AA$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AA$9))</f>
-        <v>0.99990128433921099</v>
+        <v>0.97416362824123981</v>
       </c>
       <c r="AB17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AB$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AB$9))</f>
-        <v>0.99995336698747117</v>
+        <v>0.98249498325109563</v>
       </c>
       <c r="AC17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AC$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AC$9))</f>
-        <v>0.99997797144710843</v>
+        <v>0.98818077464538168</v>
       </c>
       <c r="AD17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AD$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AD$9))</f>
-        <v>0.99998959429722678</v>
+        <v>0.9920385585064766</v>
       </c>
       <c r="AE17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AE$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AE$9))</f>
-        <v>0.99999508466031828</v>
+        <v>0.99464571926057221</v>
       </c>
       <c r="AF17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AF$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AF$9))</f>
-        <v>0.99999767815041185</v>
+        <v>0.99640298147124717</v>
       </c>
       <c r="AG17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AG$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AG$9))</f>
-        <v>0.99999890323423446</v>
+        <v>0.99758526694023342</v>
       </c>
       <c r="AH17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AH$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AH$9))</f>
-        <v>0.99999948192416133</v>
+        <v>0.99837974368876004</v>
       </c>
       <c r="AI17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AI$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AI$9))</f>
-        <v>0.99999975527821849</v>
+        <v>0.99891318403965701</v>
       </c>
       <c r="AJ17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AJ$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AJ$9))</f>
-        <v>0.99999988440159693</v>
+        <v>0.99927115904447961</v>
       </c>
       <c r="AK17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AK$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AK$9))</f>
-        <v>0.99999994539517689</v>
+        <v>0.99951129651245263</v>
       </c>
       <c r="AL17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AL$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AL$9))</f>
-        <v>0.99999997420650688</v>
+        <v>0.99967234626801127</v>
       </c>
     </row>
     <row r="18" spans="1:38" x14ac:dyDescent="0.35">
@@ -64538,11 +65487,11 @@
       </c>
       <c r="K24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:K$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,K$9))</f>
-        <v>0.60439477705223721</v>
+        <v>0.60875250837445216</v>
       </c>
       <c r="L24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:L$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,L$9))</f>
-        <v>0.60919094796401019</v>
+        <v>0.61291818587938018</v>
       </c>
       <c r="M24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:M$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,M$9))</f>
@@ -64550,103 +65499,103 @@
       </c>
       <c r="N24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:N$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,N$9))</f>
-        <v>0.63813978595964382</v>
+        <v>0.62765536813733869</v>
       </c>
       <c r="O24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:O$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,O$9))</f>
-        <v>0.6729702095225425</v>
+        <v>0.63990019564787404</v>
       </c>
       <c r="P24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:P$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,P$9))</f>
-        <v>0.72832852032984285</v>
+        <v>0.65674042596019511</v>
       </c>
       <c r="Q24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:Q$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,Q$9))</f>
-        <v>0.8</v>
+        <v>0.67912644457656723</v>
       </c>
       <c r="R24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:R$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,R$9))</f>
-        <v>0.87167147967015723</v>
+        <v>0.707576568547998</v>
       </c>
       <c r="S24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:S$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,S$9))</f>
-        <v>0.92702979047745737</v>
+        <v>0.74173747750968178</v>
       </c>
       <c r="T24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:T$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,T$9))</f>
-        <v>0.96186021404035627</v>
+        <v>0.78006640107500891</v>
       </c>
       <c r="U24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:U$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,U$9))</f>
-        <v>0.9810296507289733</v>
+        <v>0.81993359892499118</v>
       </c>
       <c r="V24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:V$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,V$9))</f>
-        <v>0.99080905203598979</v>
+        <v>0.8582625224903182</v>
       </c>
       <c r="W24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:W$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,W$9))</f>
-        <v>0.99560522294776277</v>
+        <v>0.89242343145200187</v>
       </c>
       <c r="X24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:X$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,X$9))</f>
-        <v>0.99791194972257657</v>
+        <v>0.92087355542343274</v>
       </c>
       <c r="Y24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:Y$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,Y$9))</f>
-        <v>0.99901095073734614</v>
+        <v>0.94325957403980487</v>
       </c>
       <c r="Z24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:Z$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,Z$9))</f>
-        <v>0.99953219589397779</v>
+        <v>0.96009980435212594</v>
       </c>
       <c r="AA24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AA$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AA$9))</f>
-        <v>0.99977888854523056</v>
+        <v>0.97234463186266129</v>
       </c>
       <c r="AB24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AB$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AB$9))</f>
-        <v>0.99989552387236169</v>
+        <v>0.9810296507289733</v>
       </c>
       <c r="AC24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AC$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AC$9))</f>
-        <v>0.9999506421696055</v>
+        <v>0.9870818141206199</v>
       </c>
       <c r="AD24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AD$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AD$9))</f>
-        <v>0.99997668349373559</v>
+        <v>0.99124749162554782</v>
       </c>
       <c r="AE24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AE$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AE$9))</f>
-        <v>0.99998898572355421</v>
+        <v>0.99409038732269073</v>
       </c>
       <c r="AF24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AF$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AF$9))</f>
-        <v>0.99999479714861339</v>
+        <v>0.9960192792532383</v>
       </c>
       <c r="AG24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AG$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AG$9))</f>
-        <v>0.99999754233015903</v>
+        <v>0.99732285963028611</v>
       </c>
       <c r="AH24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AH$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AH$9))</f>
-        <v>0.99999883907520593</v>
+        <v>0.99820149073562359</v>
       </c>
       <c r="AI24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AI$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AI$9))</f>
-        <v>0.99999945161711723</v>
+        <v>0.99879263347011671</v>
       </c>
       <c r="AJ24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AJ$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AJ$9))</f>
-        <v>0.99999974096208066</v>
+        <v>0.99918987184438002</v>
       </c>
       <c r="AK24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AK$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AK$9))</f>
-        <v>0.99999987763910925</v>
+        <v>0.99945659201982839</v>
       </c>
       <c r="AL24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AL$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AL$9))</f>
-        <v>0.99999994220079846</v>
+        <v>0.9996355795222398</v>
       </c>
     </row>
     <row r="25" spans="1:38" x14ac:dyDescent="0.35">
@@ -72182,7 +73131,7 @@
       </c>
       <c r="J80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:J$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,J$9))</f>
-        <v>2.2977369910025615E-2</v>
+        <v>3.2295464698450495E-2</v>
       </c>
       <c r="K80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:K$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,K$9))</f>
@@ -72190,111 +73139,111 @@
       </c>
       <c r="L80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:L$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,L$9))</f>
-        <v>9.534946489910949E-2</v>
+        <v>6.9138420343346815E-2</v>
       </c>
       <c r="M80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:M$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,M$9))</f>
-        <v>0.18242552380635635</v>
+        <v>9.9750489119685135E-2</v>
       </c>
       <c r="N80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:N$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,N$9))</f>
-        <v>0.32082130082460703</v>
+        <v>0.14185106490048777</v>
       </c>
       <c r="O80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:O$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,O$9))</f>
-        <v>0.5</v>
+        <v>0.19781611144141822</v>
       </c>
       <c r="P80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:P$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,P$9))</f>
-        <v>0.67917869917539297</v>
+        <v>0.2689414213699951</v>
       </c>
       <c r="Q80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Q$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Q$9))</f>
-        <v>0.81757447619364365</v>
+        <v>0.35434369377420455</v>
       </c>
       <c r="R80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:R$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,R$9))</f>
-        <v>0.90465053510089055</v>
+        <v>0.45016600268752216</v>
       </c>
       <c r="S80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:S$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,S$9))</f>
-        <v>0.95257412682243336</v>
+        <v>0.54983399731247795</v>
       </c>
       <c r="T80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:T$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,T$9))</f>
-        <v>0.97702263008997436</v>
+        <v>0.6456563062257954</v>
       </c>
       <c r="U80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:U$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,U$9))</f>
-        <v>0.98901305736940681</v>
+        <v>0.7310585786300049</v>
       </c>
       <c r="V80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:V$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,V$9))</f>
-        <v>0.99477987430644166</v>
+        <v>0.8021838885585818</v>
       </c>
       <c r="W80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:W$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,W$9))</f>
-        <v>0.99752737684336534</v>
+        <v>0.85814893509951229</v>
       </c>
       <c r="X80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:X$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,X$9))</f>
-        <v>0.99883048973494448</v>
+        <v>0.9002495108803148</v>
       </c>
       <c r="Y80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Y$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Y$9))</f>
-        <v>0.9994472213630764</v>
+        <v>0.93086157965665328</v>
       </c>
       <c r="Z80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Z$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Z$9))</f>
-        <v>0.99973880968090434</v>
+        <v>0.95257412682243336</v>
       </c>
       <c r="AA80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AA$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AA$9))</f>
-        <v>0.99987660542401369</v>
+        <v>0.96770453530154954</v>
       </c>
       <c r="AB80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AB$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AB$9))</f>
-        <v>0.99994170873433885</v>
+        <v>0.97811872906386943</v>
       </c>
       <c r="AC80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AC$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AC$9))</f>
-        <v>0.99997246430888531</v>
+        <v>0.98522596830672693</v>
       </c>
       <c r="AD80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AD$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AD$9))</f>
-        <v>0.99998699287153348</v>
+        <v>0.99004819813309575</v>
       </c>
       <c r="AE80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AE$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AE$9))</f>
-        <v>0.99999385582539779</v>
+        <v>0.99330714907571527</v>
       </c>
       <c r="AF80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AF$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AF$9))</f>
-        <v>0.99999709768801481</v>
+        <v>0.99550372683905886</v>
       </c>
       <c r="AG80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AG$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AG$9))</f>
-        <v>0.99999862904279302</v>
+        <v>0.99698158367529166</v>
       </c>
       <c r="AH80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AH$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AH$9))</f>
-        <v>0.99999935240520166</v>
+        <v>0.9979746796109501</v>
       </c>
       <c r="AI80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AI$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AI$9))</f>
-        <v>0.99999969409777301</v>
+        <v>0.9986414800495711</v>
       </c>
       <c r="AJ80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AJ$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AJ$9))</f>
-        <v>0.99999985550199622</v>
+        <v>0.9990889488055994</v>
       </c>
       <c r="AK80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AK$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AK$9))</f>
-        <v>0.99999993174397095</v>
+        <v>0.99938912064056562</v>
       </c>
       <c r="AL80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AL$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AL$9))</f>
-        <v>0.9999999677581336</v>
+        <v>0.99959043283501392</v>
       </c>
     </row>
     <row r="81" spans="1:38" x14ac:dyDescent="0.35">
